--- a/docs/templates/ai-import-template.xlsx
+++ b/docs/templates/ai-import-template.xlsx
@@ -130,10 +130,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,7 +692,9 @@
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="6" width="12" customWidth="1"/>
+    <col min="1" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -706,7 +710,7 @@
       <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -726,7 +730,7 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
@@ -746,7 +750,7 @@
       <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
@@ -766,7 +770,7 @@
       <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
@@ -786,7 +790,7 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
@@ -806,7 +810,7 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F6" t="s">
@@ -826,7 +830,7 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
@@ -846,7 +850,7 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
@@ -866,7 +870,7 @@
       <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
@@ -886,7 +890,7 @@
       <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
@@ -906,7 +910,7 @@
       <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
@@ -926,7 +930,7 @@
       <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
@@ -946,7 +950,7 @@
       <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
@@ -966,7 +970,7 @@
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
@@ -986,7 +990,7 @@
       <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F15" t="s">
@@ -1006,7 +1010,7 @@
       <c r="D16" t="s">
         <v>12</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F16" t="s">
@@ -1026,7 +1030,7 @@
       <c r="D17" t="s">
         <v>12</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
@@ -1046,7 +1050,7 @@
       <c r="D18" t="s">
         <v>12</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F18" t="s">
@@ -1066,7 +1070,7 @@
       <c r="D19" t="s">
         <v>12</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F19" t="s">
@@ -1086,7 +1090,7 @@
       <c r="D20" t="s">
         <v>12</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F20" t="s">
@@ -1106,7 +1110,7 @@
       <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
@@ -1126,7 +1130,7 @@
       <c r="D22" t="s">
         <v>12</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F22" t="s">
@@ -1146,7 +1150,7 @@
       <c r="D23" t="s">
         <v>12</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
@@ -1166,7 +1170,7 @@
       <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F24" t="s">
@@ -1186,7 +1190,7 @@
       <c r="D25" t="s">
         <v>12</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F25" t="s">
@@ -1206,7 +1210,7 @@
       <c r="D26" t="s">
         <v>12</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F26" t="s">
@@ -1226,7 +1230,7 @@
       <c r="D27" t="s">
         <v>12</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
@@ -1246,7 +1250,7 @@
       <c r="D28" t="s">
         <v>12</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F28" t="s">
@@ -1266,7 +1270,7 @@
       <c r="D29" t="s">
         <v>12</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F29" t="s">
@@ -1286,7 +1290,7 @@
       <c r="D30" t="s">
         <v>12</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F30" t="s">
@@ -1306,7 +1310,7 @@
       <c r="D31" t="s">
         <v>12</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F31" t="s">
@@ -1326,7 +1330,7 @@
       <c r="D32" t="s">
         <v>12</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F32" t="s">
@@ -1346,7 +1350,7 @@
       <c r="D33" t="s">
         <v>12</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F33" t="s">
@@ -1366,7 +1370,7 @@
       <c r="D34" t="s">
         <v>12</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F34" t="s">
@@ -1386,7 +1390,7 @@
       <c r="D35" t="s">
         <v>12</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F35" t="s">
@@ -1406,7 +1410,7 @@
       <c r="D36" t="s">
         <v>12</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F36" t="s">
@@ -1426,7 +1430,7 @@
       <c r="D37" t="s">
         <v>12</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F37" t="s">
@@ -1446,7 +1450,7 @@
       <c r="D38" t="s">
         <v>12</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F38" t="s">
@@ -1466,7 +1470,7 @@
       <c r="D39" t="s">
         <v>12</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F39" t="s">
@@ -1486,7 +1490,7 @@
       <c r="D40" t="s">
         <v>12</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F40" t="s">
@@ -1506,7 +1510,7 @@
       <c r="D41" t="s">
         <v>12</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F41" t="s">
@@ -1526,7 +1530,7 @@
       <c r="D42" t="s">
         <v>12</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F42" t="s">
@@ -1546,7 +1550,7 @@
       <c r="D43" t="s">
         <v>12</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F43" t="s">
@@ -1566,7 +1570,7 @@
       <c r="D44" t="s">
         <v>12</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="s">
